--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260828.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260828.xlsx
@@ -1107,17 +1107,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>玉山金</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>45,571,739</t>
+          <t>372,559,682</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>玉山金</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>372,559,682</t>
+          <t>26,584,760</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>26,584,760</t>
+          <t>45,571,739</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>115,287,320</t>
+          <t>1,327,323</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>1,327,323</t>
+          <t>17,755,952</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>17,755,952</t>
+          <t>115,287,320</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
